--- a/output/pdf_financials_xlsx/COMT.xlsx
+++ b/output/pdf_financials_xlsx/COMT.xlsx
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.171155</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.171155</v>
       </c>
     </row>
     <row r="93">
@@ -2644,7 +2644,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.171155</v>
       </c>

--- a/output/pdf_financials_xlsx/COMT.xlsx
+++ b/output/pdf_financials_xlsx/COMT.xlsx
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055099</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.066749</v>
       </c>
     </row>
     <row r="35">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055099</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.066749</v>
       </c>
     </row>
     <row r="37">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.269727</v>
+        <v>0.214628</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.11797</v>
+        <v>0.051221</v>
       </c>
     </row>
     <row r="49">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/COMT.xlsx
+++ b/output/pdf_financials_xlsx/COMT.xlsx
@@ -3156,7 +3156,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
